--- a/rtss-pre1917/charts/birth-death-counts/raw-sources/Костромская.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/raw-sources/Костромская.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t xml:space="preserve">Числа рождений и смертей для </t>
   </si>
